--- a/49_Kuroshio_Current/49_(2019)_extracted/49_10049_Kuroshio_Current_(2013)_reconstructed.xlsx
+++ b/49_Kuroshio_Current/49_(2019)_extracted/49_10049_Kuroshio_Current_(2013)_reconstructed.xlsx
@@ -9045,17 +9045,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Detritus (OF)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Detritus (KC)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Detritus (OYC)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Detritus (KC)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Detritus (OF)</t>
         </is>
       </c>
     </row>
